--- a/research/traditional_assets/database/data/nigeria/nigeria_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_banks_regional.xlsx
@@ -587,6 +587,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.261</v>
+      </c>
+      <c r="E2">
+        <v>0.404</v>
+      </c>
       <c r="G2">
         <v>0</v>
       </c>
@@ -600,82 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>9.67</v>
+        <v>10.9</v>
       </c>
       <c r="L2">
-        <v>0.2460559796437659</v>
+        <v>0.2334047109207709</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.07602256699576868</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.4944954128440366</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.07602256699576868</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.4944954128440366</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>67.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="V2">
-        <v>1.447761194029851</v>
+        <v>1.097320169252468</v>
       </c>
       <c r="W2">
-        <v>0.2518229166666667</v>
+        <v>0.219758064516129</v>
       </c>
       <c r="X2">
-        <v>0.1311279009852544</v>
+        <v>0.1534525440219696</v>
       </c>
       <c r="Y2">
-        <v>0.1206950156814122</v>
+        <v>0.06630552049415947</v>
       </c>
       <c r="Z2">
-        <v>1.212962962962963</v>
+        <v>1.225721784776903</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08811755276648532</v>
+        <v>0.1223991131716346</v>
       </c>
       <c r="AC2">
-        <v>-0.08811755276648532</v>
+        <v>-0.1223991131716346</v>
       </c>
       <c r="AD2">
-        <v>56.4</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>56.4</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>-11.50000000000001</v>
+        <v>8.299999999999997</v>
       </c>
       <c r="AH2">
-        <v>0.5459825750242013</v>
+        <v>0.5484076433121019</v>
       </c>
       <c r="AI2">
-        <v>0.5320754716981132</v>
+        <v>0.6194244604316547</v>
       </c>
       <c r="AJ2">
-        <v>-0.3248587570621472</v>
+        <v>0.1047979797979798</v>
       </c>
       <c r="AK2">
-        <v>-0.3018372703412076</v>
+        <v>0.1356209150326797</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -700,6 +709,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.261</v>
+      </c>
+      <c r="E3">
+        <v>0.404</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -713,82 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>9.67</v>
+        <v>10.9</v>
       </c>
       <c r="L3">
-        <v>0.2460559796437659</v>
+        <v>0.2334047109207709</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>5.39</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.07602256699576868</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.4944954128440366</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>5.39</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07602256699576868</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.4944954128440366</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>67.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="V3">
-        <v>1.447761194029851</v>
+        <v>1.097320169252468</v>
       </c>
       <c r="W3">
-        <v>0.2518229166666667</v>
+        <v>0.219758064516129</v>
       </c>
       <c r="X3">
-        <v>0.1311279009852544</v>
+        <v>0.1534525440219696</v>
       </c>
       <c r="Y3">
-        <v>0.1206950156814122</v>
+        <v>0.06630552049415947</v>
       </c>
       <c r="Z3">
-        <v>1.212962962962963</v>
+        <v>1.225721784776903</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08811755276648532</v>
+        <v>0.1223991131716346</v>
       </c>
       <c r="AC3">
-        <v>-0.08811755276648532</v>
+        <v>-0.1223991131716346</v>
       </c>
       <c r="AD3">
-        <v>56.4</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>56.4</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>-11.50000000000001</v>
+        <v>8.299999999999997</v>
       </c>
       <c r="AH3">
-        <v>0.5459825750242013</v>
+        <v>0.5484076433121019</v>
       </c>
       <c r="AI3">
-        <v>0.5320754716981132</v>
+        <v>0.6194244604316547</v>
       </c>
       <c r="AJ3">
-        <v>-0.3248587570621472</v>
+        <v>0.1047979797979798</v>
       </c>
       <c r="AK3">
-        <v>-0.3018372703412076</v>
+        <v>0.1356209150326797</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/nigeria/nigeria_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.261</v>
+        <v>0.3175</v>
       </c>
       <c r="E2">
-        <v>0.404</v>
+        <v>1.1995</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>10.9</v>
+        <v>13.659</v>
       </c>
       <c r="L2">
-        <v>0.2334047109207709</v>
+        <v>0.3423308270676692</v>
       </c>
       <c r="M2">
-        <v>5.39</v>
+        <v>2.209</v>
       </c>
       <c r="N2">
-        <v>0.07602256699576868</v>
+        <v>0.0239587852494577</v>
       </c>
       <c r="O2">
-        <v>0.4944954128440366</v>
+        <v>0.1617248700490519</v>
       </c>
       <c r="P2">
-        <v>5.39</v>
+        <v>2.209</v>
       </c>
       <c r="Q2">
-        <v>0.07602256699576868</v>
+        <v>0.0239587852494577</v>
       </c>
       <c r="R2">
-        <v>0.4944954128440366</v>
+        <v>0.1617248700490519</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>77.8</v>
+        <v>125.71</v>
       </c>
       <c r="V2">
-        <v>1.097320169252468</v>
+        <v>1.363449023861171</v>
       </c>
       <c r="W2">
-        <v>0.219758064516129</v>
+        <v>0.1844246411249452</v>
       </c>
       <c r="X2">
-        <v>0.1534525440219696</v>
+        <v>0.1002689953332412</v>
       </c>
       <c r="Y2">
-        <v>0.06630552049415947</v>
+        <v>0.08415564579170401</v>
       </c>
       <c r="Z2">
-        <v>1.225721784776903</v>
+        <v>0.5621301775147929</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1223991131716346</v>
+        <v>0.0972268072529687</v>
       </c>
       <c r="AC2">
-        <v>-0.1223991131716346</v>
+        <v>-0.0972268072529687</v>
       </c>
       <c r="AD2">
-        <v>86.09999999999999</v>
+        <v>60.36</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>86.09999999999999</v>
+        <v>60.36</v>
       </c>
       <c r="AG2">
-        <v>8.299999999999997</v>
+        <v>-65.34999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5484076433121019</v>
+        <v>0.3956476140534871</v>
       </c>
       <c r="AI2">
-        <v>0.6194244604316547</v>
+        <v>0.5971507716660072</v>
       </c>
       <c r="AJ2">
-        <v>0.1047979797979798</v>
+        <v>-2.433891992551209</v>
       </c>
       <c r="AK2">
-        <v>0.1356209150326797</v>
+        <v>2.653268371904182</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,117 +701,239 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Livingtrust Mortgage Bank PLC (NGSE:LTBNG)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.29</v>
+      </c>
+      <c r="E3">
+        <v>0.34</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0.859</v>
+      </c>
+      <c r="L3">
+        <v>0.3436</v>
+      </c>
+      <c r="M3">
+        <v>0.079</v>
+      </c>
+      <c r="N3">
+        <v>0.004702380952380952</v>
+      </c>
+      <c r="O3">
+        <v>0.0919674039580908</v>
+      </c>
+      <c r="P3">
+        <v>0.079</v>
+      </c>
+      <c r="Q3">
+        <v>0.004702380952380952</v>
+      </c>
+      <c r="R3">
+        <v>0.0919674039580908</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>4.41</v>
+      </c>
+      <c r="V3">
+        <v>0.2625</v>
+      </c>
+      <c r="W3">
+        <v>0.1268833087149188</v>
+      </c>
+      <c r="X3">
+        <v>0.09244795933389027</v>
+      </c>
+      <c r="Y3">
+        <v>0.03443534938102849</v>
+      </c>
+      <c r="Z3">
+        <v>0.2556237218813905</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.09289370010078457</v>
+      </c>
+      <c r="AC3">
+        <v>-0.09289370010078457</v>
+      </c>
+      <c r="AD3">
+        <v>4.26</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>4.26</v>
+      </c>
+      <c r="AG3">
+        <v>-0.1500000000000004</v>
+      </c>
+      <c r="AH3">
+        <v>0.2022792022792022</v>
+      </c>
+      <c r="AI3">
+        <v>0.4743875278396436</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.009009009009009031</v>
+      </c>
+      <c r="AK3">
+        <v>-0.03282275711159745</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Jaiz Bank Plc (NGSE:JAIZBANK)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.261</v>
-      </c>
-      <c r="E3">
-        <v>0.404</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>10.9</v>
-      </c>
-      <c r="L3">
-        <v>0.2334047109207709</v>
-      </c>
-      <c r="M3">
-        <v>5.39</v>
-      </c>
-      <c r="N3">
-        <v>0.07602256699576868</v>
-      </c>
-      <c r="O3">
-        <v>0.4944954128440366</v>
-      </c>
-      <c r="P3">
-        <v>5.39</v>
-      </c>
-      <c r="Q3">
-        <v>0.07602256699576868</v>
-      </c>
-      <c r="R3">
-        <v>0.4944954128440366</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>77.8</v>
-      </c>
-      <c r="V3">
-        <v>1.097320169252468</v>
-      </c>
-      <c r="W3">
-        <v>0.219758064516129</v>
-      </c>
-      <c r="X3">
-        <v>0.1534525440219696</v>
-      </c>
-      <c r="Y3">
-        <v>0.06630552049415947</v>
-      </c>
-      <c r="Z3">
-        <v>1.225721784776903</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.1223991131716346</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1223991131716346</v>
-      </c>
-      <c r="AD3">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="AG3">
-        <v>8.299999999999997</v>
-      </c>
-      <c r="AH3">
-        <v>0.5484076433121019</v>
-      </c>
-      <c r="AI3">
-        <v>0.6194244604316547</v>
-      </c>
-      <c r="AJ3">
-        <v>0.1047979797979798</v>
-      </c>
-      <c r="AK3">
-        <v>0.1356209150326797</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="D4">
+        <v>0.345</v>
+      </c>
+      <c r="E4">
+        <v>2.059</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>12.8</v>
+      </c>
+      <c r="L4">
+        <v>0.3422459893048129</v>
+      </c>
+      <c r="M4">
+        <v>2.13</v>
+      </c>
+      <c r="N4">
+        <v>0.02824933687002652</v>
+      </c>
+      <c r="O4">
+        <v>0.16640625</v>
+      </c>
+      <c r="P4">
+        <v>2.13</v>
+      </c>
+      <c r="Q4">
+        <v>0.02824933687002652</v>
+      </c>
+      <c r="R4">
+        <v>0.16640625</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>121.3</v>
+      </c>
+      <c r="V4">
+        <v>1.608753315649867</v>
+      </c>
+      <c r="W4">
+        <v>0.2419659735349717</v>
+      </c>
+      <c r="X4">
+        <v>0.1080900313325922</v>
+      </c>
+      <c r="Y4">
+        <v>0.1338759422023795</v>
+      </c>
+      <c r="Z4">
+        <v>0.611111111111111</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.1015599144051528</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1015599144051528</v>
+      </c>
+      <c r="AD4">
+        <v>56.1</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>56.1</v>
+      </c>
+      <c r="AG4">
+        <v>-65.19999999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.4266159695817491</v>
+      </c>
+      <c r="AI4">
+        <v>0.6091205211726385</v>
+      </c>
+      <c r="AJ4">
+        <v>-6.392156862745086</v>
+      </c>
+      <c r="AK4">
+        <v>2.232876712328768</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>
